--- a/data/gravel/Esker Japhy 2025.xlsx
+++ b/data/gravel/Esker Japhy 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBC1F49-FF25-1A4F-BCEA-6827A74CC6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0403A3A-F857-2F4D-A3DD-605F583FD898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12440" yWindow="2580" windowWidth="26100" windowHeight="15020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -383,18 +383,6 @@
     <t>https://eskercycles.com/cdn/shop/files/CY25JaphyMetalFlakeorangeComplete-1_1.jpg?v=1741569859&amp;width=1200</t>
   </si>
   <si>
-    <t>S1/SM </t>
-  </si>
-  <si>
-    <t>S2/MD </t>
-  </si>
-  <si>
-    <t>S3/LG </t>
-  </si>
-  <si>
-    <t>S4/XL </t>
-  </si>
-  <si>
     <t>430-444</t>
   </si>
   <si>
@@ -417,6 +405,18 @@
   </si>
   <si>
     <t>frame only</t>
+  </si>
+  <si>
+    <t>S1/SM</t>
+  </si>
+  <si>
+    <t>S2/MD</t>
+  </si>
+  <si>
+    <t>S3/LG</t>
+  </si>
+  <si>
+    <t>S4/XL</t>
   </si>
 </sst>
 </file>
@@ -863,19 +863,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -898,7 +898,7 @@
         <v>660</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1057,16 +1057,16 @@
         <v>430</v>
       </c>
       <c r="G17" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H17" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I17" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="J17" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -1399,7 +1399,7 @@
         <v>90</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -1426,7 +1426,7 @@
         <v>109</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -1541,7 +1541,7 @@
         <v>108</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -1596,7 +1596,7 @@
         <v>54</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -1670,7 +1670,7 @@
         <v>1100</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
